--- a/Pandas_tips_tricks/awen_wala_data.xlsx
+++ b/Pandas_tips_tricks/awen_wala_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,114 +417,114 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>PROVINCE</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>DIVISION</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRICT</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>SUB DIVISION</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>AREA (sq.km)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>ALL SEXES (RURAL)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>MALE (RURAL)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>FEMALE (RURAL)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>TRANSGENDER (RURAL)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>SEX RATIO (RURAL)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>AVG HOUSEHOLD SIZE (RURAL)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>POPULATION 1998 (RURAL)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ANNUAL GROWTH RATE (RURAL)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>ALL SEXES (URBAN)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>MALE (URBAN)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>FEMALE (URBAN)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>TRANSGENDER (URBAN)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>SEX RATIO (URBAN)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>AVG HOUSEHOLD SIZE (URBAN)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>POPULATION 1998 (URBAN)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>ANNUAL GROWTH RATE (URBAN)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" t="n">
         <v>0</v>
       </c>
       <c r="B2" t="inlineStr">
@@ -612,7 +600,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" t="n">
         <v>1</v>
       </c>
       <c r="B3" t="inlineStr">
@@ -688,7 +676,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" t="n">
         <v>2</v>
       </c>
       <c r="B4" t="inlineStr">
@@ -764,7 +752,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" t="n">
         <v>3</v>
       </c>
       <c r="B5" t="inlineStr">
@@ -840,7 +828,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" t="n">
         <v>4</v>
       </c>
       <c r="B6" t="inlineStr">
@@ -916,7 +904,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" t="n">
         <v>5</v>
       </c>
       <c r="B7" t="inlineStr">
@@ -992,7 +980,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" t="n">
         <v>6</v>
       </c>
       <c r="B8" t="inlineStr">
@@ -1068,7 +1056,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" t="n">
         <v>7</v>
       </c>
       <c r="B9" t="inlineStr">
@@ -1144,7 +1132,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" t="n">
         <v>8</v>
       </c>
       <c r="B10" t="inlineStr">
@@ -1220,7 +1208,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" t="n">
         <v>9</v>
       </c>
       <c r="B11" t="inlineStr">
@@ -1296,7 +1284,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" t="n">
         <v>10</v>
       </c>
       <c r="B12" t="inlineStr">
@@ -1372,7 +1360,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" t="n">
         <v>11</v>
       </c>
       <c r="B13" t="inlineStr">
@@ -1448,7 +1436,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" t="n">
         <v>12</v>
       </c>
       <c r="B14" t="inlineStr">
@@ -1524,7 +1512,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" t="n">
         <v>13</v>
       </c>
       <c r="B15" t="inlineStr">
@@ -1600,7 +1588,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" t="n">
         <v>14</v>
       </c>
       <c r="B16" t="inlineStr">
@@ -1676,7 +1664,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" t="n">
         <v>15</v>
       </c>
       <c r="B17" t="inlineStr">
@@ -1752,7 +1740,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" t="n">
         <v>16</v>
       </c>
       <c r="B18" t="inlineStr">
@@ -1828,7 +1816,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" t="n">
         <v>17</v>
       </c>
       <c r="B19" t="inlineStr">
@@ -1904,7 +1892,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" t="n">
         <v>18</v>
       </c>
       <c r="B20" t="inlineStr">
@@ -1980,7 +1968,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" t="n">
         <v>19</v>
       </c>
       <c r="B21" t="inlineStr">
@@ -2056,7 +2044,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" t="n">
         <v>20</v>
       </c>
       <c r="B22" t="inlineStr">
@@ -2132,7 +2120,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" t="n">
         <v>21</v>
       </c>
       <c r="B23" t="inlineStr">
@@ -2208,7 +2196,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" t="n">
         <v>22</v>
       </c>
       <c r="B24" t="inlineStr">
@@ -2284,7 +2272,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" t="n">
         <v>23</v>
       </c>
       <c r="B25" t="inlineStr">
@@ -2360,7 +2348,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" t="n">
         <v>24</v>
       </c>
       <c r="B26" t="inlineStr">
@@ -2436,7 +2424,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" t="n">
         <v>25</v>
       </c>
       <c r="B27" t="inlineStr">
@@ -2512,7 +2500,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" t="n">
         <v>26</v>
       </c>
       <c r="B28" t="inlineStr">
@@ -2588,7 +2576,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" t="n">
         <v>27</v>
       </c>
       <c r="B29" t="inlineStr">
@@ -2664,7 +2652,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" t="n">
         <v>28</v>
       </c>
       <c r="B30" t="inlineStr">
@@ -2740,7 +2728,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" t="n">
         <v>29</v>
       </c>
       <c r="B31" t="inlineStr">
@@ -2816,7 +2804,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" t="n">
         <v>30</v>
       </c>
       <c r="B32" t="inlineStr">
@@ -2892,7 +2880,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" t="n">
         <v>31</v>
       </c>
       <c r="B33" t="inlineStr">
@@ -2968,7 +2956,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
       <c r="B34" t="inlineStr">
@@ -3044,7 +3032,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" t="n">
         <v>33</v>
       </c>
       <c r="B35" t="inlineStr">
@@ -3120,7 +3108,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" t="n">
         <v>34</v>
       </c>
       <c r="B36" t="inlineStr">
@@ -3196,7 +3184,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" t="n">
         <v>35</v>
       </c>
       <c r="B37" t="inlineStr">
@@ -3272,7 +3260,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" t="n">
         <v>36</v>
       </c>
       <c r="B38" t="inlineStr">
@@ -3348,7 +3336,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" t="n">
         <v>37</v>
       </c>
       <c r="B39" t="inlineStr">
@@ -3424,7 +3412,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" t="n">
         <v>38</v>
       </c>
       <c r="B40" t="inlineStr">
@@ -3500,7 +3488,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" t="n">
         <v>39</v>
       </c>
       <c r="B41" t="inlineStr">
@@ -3576,7 +3564,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" t="n">
         <v>40</v>
       </c>
       <c r="B42" t="inlineStr">
@@ -3652,7 +3640,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" t="n">
         <v>41</v>
       </c>
       <c r="B43" t="inlineStr">
@@ -3728,7 +3716,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" t="n">
         <v>42</v>
       </c>
       <c r="B44" t="inlineStr">
@@ -3804,7 +3792,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" t="n">
         <v>43</v>
       </c>
       <c r="B45" t="inlineStr">
@@ -3880,7 +3868,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" t="n">
         <v>44</v>
       </c>
       <c r="B46" t="inlineStr">
@@ -3956,7 +3944,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" t="n">
         <v>45</v>
       </c>
       <c r="B47" t="inlineStr">
@@ -4032,7 +4020,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" t="n">
         <v>46</v>
       </c>
       <c r="B48" t="inlineStr">
@@ -4108,7 +4096,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" t="n">
         <v>47</v>
       </c>
       <c r="B49" t="inlineStr">
@@ -4184,7 +4172,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" t="n">
         <v>48</v>
       </c>
       <c r="B50" t="inlineStr">
@@ -4260,7 +4248,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" t="n">
         <v>49</v>
       </c>
       <c r="B51" t="inlineStr">
@@ -4336,7 +4324,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" t="n">
         <v>50</v>
       </c>
       <c r="B52" t="inlineStr">
@@ -4412,7 +4400,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" t="n">
         <v>51</v>
       </c>
       <c r="B53" t="inlineStr">
@@ -4488,7 +4476,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" t="n">
         <v>52</v>
       </c>
       <c r="B54" t="inlineStr">
@@ -4564,7 +4552,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" t="n">
         <v>53</v>
       </c>
       <c r="B55" t="inlineStr">
@@ -4640,7 +4628,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" t="n">
         <v>54</v>
       </c>
       <c r="B56" t="inlineStr">
@@ -4716,7 +4704,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" t="n">
         <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
@@ -4792,7 +4780,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" t="n">
         <v>56</v>
       </c>
       <c r="B58" t="inlineStr">
@@ -4868,7 +4856,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" t="n">
         <v>57</v>
       </c>
       <c r="B59" t="inlineStr">
@@ -4944,7 +4932,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" t="n">
         <v>58</v>
       </c>
       <c r="B60" t="inlineStr">
@@ -5020,7 +5008,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" t="n">
         <v>59</v>
       </c>
       <c r="B61" t="inlineStr">
@@ -5096,7 +5084,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" t="n">
         <v>60</v>
       </c>
       <c r="B62" t="inlineStr">
@@ -5172,7 +5160,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" t="n">
         <v>61</v>
       </c>
       <c r="B63" t="inlineStr">
@@ -5248,7 +5236,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" t="n">
         <v>62</v>
       </c>
       <c r="B64" t="inlineStr">
@@ -5324,7 +5312,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" t="n">
         <v>63</v>
       </c>
       <c r="B65" t="inlineStr">
@@ -5400,7 +5388,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" t="n">
         <v>64</v>
       </c>
       <c r="B66" t="inlineStr">
@@ -5476,7 +5464,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" t="n">
         <v>65</v>
       </c>
       <c r="B67" t="inlineStr">
@@ -5552,7 +5540,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" t="n">
         <v>66</v>
       </c>
       <c r="B68" t="inlineStr">
@@ -5628,7 +5616,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" t="n">
         <v>67</v>
       </c>
       <c r="B69" t="inlineStr">
@@ -5704,7 +5692,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" t="n">
         <v>68</v>
       </c>
       <c r="B70" t="inlineStr">
@@ -5780,7 +5768,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" t="n">
         <v>69</v>
       </c>
       <c r="B71" t="inlineStr">
@@ -5856,7 +5844,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" t="n">
         <v>70</v>
       </c>
       <c r="B72" t="inlineStr">
@@ -5932,7 +5920,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" t="n">
         <v>71</v>
       </c>
       <c r="B73" t="inlineStr">
@@ -6008,7 +5996,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" t="n">
         <v>72</v>
       </c>
       <c r="B74" t="inlineStr">
@@ -6084,7 +6072,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" t="n">
         <v>73</v>
       </c>
       <c r="B75" t="inlineStr">
@@ -6160,7 +6148,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" t="n">
         <v>74</v>
       </c>
       <c r="B76" t="inlineStr">
@@ -6236,7 +6224,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" t="n">
         <v>75</v>
       </c>
       <c r="B77" t="inlineStr">
@@ -6312,7 +6300,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" t="n">
         <v>76</v>
       </c>
       <c r="B78" t="inlineStr">
@@ -6388,7 +6376,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" t="n">
         <v>77</v>
       </c>
       <c r="B79" t="inlineStr">
@@ -6464,7 +6452,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" t="n">
         <v>78</v>
       </c>
       <c r="B80" t="inlineStr">
@@ -6540,7 +6528,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" t="n">
         <v>79</v>
       </c>
       <c r="B81" t="inlineStr">
@@ -6616,7 +6604,7 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" t="n">
         <v>80</v>
       </c>
       <c r="B82" t="inlineStr">
@@ -6692,7 +6680,7 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" t="n">
         <v>81</v>
       </c>
       <c r="B83" t="inlineStr">
@@ -6768,7 +6756,7 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" t="n">
         <v>82</v>
       </c>
       <c r="B84" t="inlineStr">
@@ -6844,7 +6832,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" t="n">
         <v>83</v>
       </c>
       <c r="B85" t="inlineStr">
@@ -6920,7 +6908,7 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" t="n">
         <v>84</v>
       </c>
       <c r="B86" t="inlineStr">
@@ -6996,7 +6984,7 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" t="n">
         <v>85</v>
       </c>
       <c r="B87" t="inlineStr">
@@ -7072,7 +7060,7 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" t="n">
         <v>86</v>
       </c>
       <c r="B88" t="inlineStr">
@@ -7148,7 +7136,7 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" t="n">
         <v>87</v>
       </c>
       <c r="B89" t="inlineStr">
@@ -7224,7 +7212,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" t="n">
         <v>88</v>
       </c>
       <c r="B90" t="inlineStr">
@@ -7300,7 +7288,7 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" t="n">
         <v>89</v>
       </c>
       <c r="B91" t="inlineStr">
@@ -7376,7 +7364,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" t="n">
         <v>90</v>
       </c>
       <c r="B92" t="inlineStr">
@@ -7452,7 +7440,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" t="n">
         <v>91</v>
       </c>
       <c r="B93" t="inlineStr">
@@ -7528,7 +7516,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" t="n">
         <v>92</v>
       </c>
       <c r="B94" t="inlineStr">
@@ -7604,7 +7592,7 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" t="n">
         <v>93</v>
       </c>
       <c r="B95" t="inlineStr">
@@ -7680,7 +7668,7 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" t="n">
         <v>94</v>
       </c>
       <c r="B96" t="inlineStr">
@@ -7756,7 +7744,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" t="n">
         <v>95</v>
       </c>
       <c r="B97" t="inlineStr">
@@ -7832,7 +7820,7 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" t="n">
         <v>96</v>
       </c>
       <c r="B98" t="inlineStr">
@@ -7908,7 +7896,7 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" t="n">
         <v>97</v>
       </c>
       <c r="B99" t="inlineStr">
@@ -7984,7 +7972,7 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" t="n">
         <v>98</v>
       </c>
       <c r="B100" t="inlineStr">
@@ -8060,7 +8048,7 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" t="n">
         <v>99</v>
       </c>
       <c r="B101" t="inlineStr">
@@ -8136,7 +8124,7 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" t="n">
         <v>100</v>
       </c>
       <c r="B102" t="inlineStr">
@@ -8212,7 +8200,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" t="n">
         <v>101</v>
       </c>
       <c r="B103" t="inlineStr">
@@ -8288,7 +8276,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" t="n">
         <v>102</v>
       </c>
       <c r="B104" t="inlineStr">
@@ -8364,7 +8352,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" t="n">
         <v>103</v>
       </c>
       <c r="B105" t="inlineStr">
@@ -8440,7 +8428,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" t="n">
         <v>104</v>
       </c>
       <c r="B106" t="inlineStr">
@@ -8516,7 +8504,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" t="n">
         <v>105</v>
       </c>
       <c r="B107" t="inlineStr">
@@ -8592,7 +8580,7 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" t="n">
         <v>106</v>
       </c>
       <c r="B108" t="inlineStr">
@@ -8668,7 +8656,7 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" t="n">
         <v>107</v>
       </c>
       <c r="B109" t="inlineStr">
@@ -8744,7 +8732,7 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" t="n">
         <v>108</v>
       </c>
       <c r="B110" t="inlineStr">
@@ -8820,7 +8808,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" t="n">
         <v>109</v>
       </c>
       <c r="B111" t="inlineStr">
@@ -8896,7 +8884,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" t="n">
         <v>110</v>
       </c>
       <c r="B112" t="inlineStr">
@@ -8972,7 +8960,7 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" t="n">
         <v>111</v>
       </c>
       <c r="B113" t="inlineStr">
@@ -9048,7 +9036,7 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" t="n">
         <v>112</v>
       </c>
       <c r="B114" t="inlineStr">
@@ -9124,7 +9112,7 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" t="n">
         <v>113</v>
       </c>
       <c r="B115" t="inlineStr">
@@ -9200,7 +9188,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" t="n">
         <v>114</v>
       </c>
       <c r="B116" t="inlineStr">
@@ -9276,7 +9264,7 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" t="n">
         <v>115</v>
       </c>
       <c r="B117" t="inlineStr">
@@ -9352,7 +9340,7 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" t="n">
         <v>116</v>
       </c>
       <c r="B118" t="inlineStr">
@@ -9428,7 +9416,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" t="n">
         <v>117</v>
       </c>
       <c r="B119" t="inlineStr">
@@ -9504,7 +9492,7 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" t="n">
         <v>118</v>
       </c>
       <c r="B120" t="inlineStr">
@@ -9580,7 +9568,7 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" t="n">
         <v>119</v>
       </c>
       <c r="B121" t="inlineStr">
@@ -9656,7 +9644,7 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" t="n">
         <v>120</v>
       </c>
       <c r="B122" t="inlineStr">
@@ -9732,7 +9720,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" t="n">
         <v>121</v>
       </c>
       <c r="B123" t="inlineStr">
@@ -9808,7 +9796,7 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" t="n">
         <v>122</v>
       </c>
       <c r="B124" t="inlineStr">
@@ -9884,7 +9872,7 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" t="n">
         <v>123</v>
       </c>
       <c r="B125" t="inlineStr">
@@ -9960,7 +9948,7 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" t="n">
         <v>124</v>
       </c>
       <c r="B126" t="inlineStr">
@@ -10036,7 +10024,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" t="n">
         <v>125</v>
       </c>
       <c r="B127" t="inlineStr">
@@ -10112,7 +10100,7 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" t="n">
         <v>126</v>
       </c>
       <c r="B128" t="inlineStr">
@@ -10188,7 +10176,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" t="n">
         <v>127</v>
       </c>
       <c r="B129" t="inlineStr">
@@ -10264,7 +10252,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" t="n">
         <v>128</v>
       </c>
       <c r="B130" t="inlineStr">
@@ -10340,7 +10328,7 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" t="n">
         <v>129</v>
       </c>
       <c r="B131" t="inlineStr">
@@ -10416,7 +10404,7 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" t="n">
         <v>130</v>
       </c>
       <c r="B132" t="inlineStr">
@@ -10492,7 +10480,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" t="n">
         <v>131</v>
       </c>
       <c r="B133" t="inlineStr">
@@ -10568,7 +10556,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" t="n">
         <v>132</v>
       </c>
       <c r="B134" t="inlineStr">
@@ -10644,7 +10632,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" t="n">
         <v>133</v>
       </c>
       <c r="B135" t="inlineStr">
@@ -10720,7 +10708,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" t="n">
         <v>134</v>
       </c>
       <c r="B136" t="inlineStr">
@@ -10796,7 +10784,7 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" t="n">
         <v>135</v>
       </c>
       <c r="B137" t="inlineStr">
@@ -10872,7 +10860,7 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" t="n">
         <v>136</v>
       </c>
       <c r="B138" t="inlineStr">
@@ -10948,7 +10936,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" t="n">
         <v>137</v>
       </c>
       <c r="B139" t="inlineStr">
@@ -11024,7 +11012,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" t="n">
         <v>138</v>
       </c>
       <c r="B140" t="inlineStr">
@@ -11100,7 +11088,7 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" t="n">
         <v>139</v>
       </c>
       <c r="B141" t="inlineStr">
@@ -11176,7 +11164,7 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" t="n">
         <v>140</v>
       </c>
       <c r="B142" t="inlineStr">
@@ -11252,7 +11240,7 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" t="n">
         <v>141</v>
       </c>
       <c r="B143" t="inlineStr">
@@ -11328,7 +11316,7 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" t="n">
         <v>142</v>
       </c>
       <c r="B144" t="inlineStr">
@@ -11404,7 +11392,7 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" t="n">
         <v>143</v>
       </c>
       <c r="B145" t="inlineStr">
@@ -11480,7 +11468,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" t="n">
         <v>144</v>
       </c>
       <c r="B146" t="inlineStr">
@@ -11556,7 +11544,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" t="n">
         <v>145</v>
       </c>
       <c r="B147" t="inlineStr">
@@ -11632,7 +11620,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" t="n">
         <v>146</v>
       </c>
       <c r="B148" t="inlineStr">
@@ -11708,7 +11696,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" t="n">
         <v>147</v>
       </c>
       <c r="B149" t="inlineStr">
@@ -11784,7 +11772,7 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" t="n">
         <v>148</v>
       </c>
       <c r="B150" t="inlineStr">
@@ -11860,7 +11848,7 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" t="n">
         <v>149</v>
       </c>
       <c r="B151" t="inlineStr">
@@ -11936,7 +11924,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" t="n">
         <v>150</v>
       </c>
       <c r="B152" t="inlineStr">
@@ -12012,7 +12000,7 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" t="n">
         <v>151</v>
       </c>
       <c r="B153" t="inlineStr">
@@ -12088,7 +12076,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" t="n">
         <v>152</v>
       </c>
       <c r="B154" t="inlineStr">
@@ -12164,7 +12152,7 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" t="n">
         <v>153</v>
       </c>
       <c r="B155" t="inlineStr">
@@ -12240,7 +12228,7 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" t="n">
         <v>154</v>
       </c>
       <c r="B156" t="inlineStr">
@@ -12316,7 +12304,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" t="n">
         <v>155</v>
       </c>
       <c r="B157" t="inlineStr">
@@ -12392,7 +12380,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" t="n">
         <v>156</v>
       </c>
       <c r="B158" t="inlineStr">
@@ -12468,7 +12456,7 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" t="n">
         <v>157</v>
       </c>
       <c r="B159" t="inlineStr">
@@ -12544,7 +12532,7 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" t="n">
         <v>158</v>
       </c>
       <c r="B160" t="inlineStr">
@@ -12620,7 +12608,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" t="n">
         <v>159</v>
       </c>
       <c r="B161" t="inlineStr">
@@ -12696,7 +12684,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" t="n">
         <v>160</v>
       </c>
       <c r="B162" t="inlineStr">
@@ -12772,7 +12760,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" t="n">
         <v>161</v>
       </c>
       <c r="B163" t="inlineStr">
@@ -12848,7 +12836,7 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" t="n">
         <v>162</v>
       </c>
       <c r="B164" t="inlineStr">
@@ -12924,7 +12912,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" t="n">
         <v>163</v>
       </c>
       <c r="B165" t="inlineStr">
@@ -13000,7 +12988,7 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" t="n">
         <v>164</v>
       </c>
       <c r="B166" t="inlineStr">
@@ -13076,7 +13064,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" t="n">
         <v>165</v>
       </c>
       <c r="B167" t="inlineStr">
@@ -13152,7 +13140,7 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" t="n">
         <v>166</v>
       </c>
       <c r="B168" t="inlineStr">
@@ -13228,7 +13216,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" t="n">
         <v>167</v>
       </c>
       <c r="B169" t="inlineStr">
@@ -13304,7 +13292,7 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" t="n">
         <v>168</v>
       </c>
       <c r="B170" t="inlineStr">
@@ -13380,7 +13368,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" t="n">
         <v>169</v>
       </c>
       <c r="B171" t="inlineStr">
@@ -13456,7 +13444,7 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" t="n">
         <v>170</v>
       </c>
       <c r="B172" t="inlineStr">
@@ -13532,7 +13520,7 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" t="n">
         <v>171</v>
       </c>
       <c r="B173" t="inlineStr">
@@ -13608,7 +13596,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" t="n">
         <v>172</v>
       </c>
       <c r="B174" t="inlineStr">
@@ -13684,7 +13672,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" t="n">
         <v>173</v>
       </c>
       <c r="B175" t="inlineStr">
@@ -13760,7 +13748,7 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" t="n">
         <v>174</v>
       </c>
       <c r="B176" t="inlineStr">
@@ -13836,7 +13824,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" t="n">
         <v>175</v>
       </c>
       <c r="B177" t="inlineStr">
@@ -13912,7 +13900,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" t="n">
         <v>176</v>
       </c>
       <c r="B178" t="inlineStr">
@@ -13988,7 +13976,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" t="n">
         <v>177</v>
       </c>
       <c r="B179" t="inlineStr">
@@ -14064,7 +14052,7 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" t="n">
         <v>178</v>
       </c>
       <c r="B180" t="inlineStr">
@@ -14140,7 +14128,7 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" t="n">
         <v>179</v>
       </c>
       <c r="B181" t="inlineStr">
@@ -14216,7 +14204,7 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" t="n">
         <v>180</v>
       </c>
       <c r="B182" t="inlineStr">
@@ -14292,7 +14280,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" t="n">
         <v>181</v>
       </c>
       <c r="B183" t="inlineStr">
@@ -14368,7 +14356,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" t="n">
         <v>182</v>
       </c>
       <c r="B184" t="inlineStr">
@@ -14444,7 +14432,7 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" t="n">
         <v>183</v>
       </c>
       <c r="B185" t="inlineStr">
@@ -14520,7 +14508,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" t="n">
         <v>184</v>
       </c>
       <c r="B186" t="inlineStr">
@@ -14596,7 +14584,7 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" t="n">
         <v>185</v>
       </c>
       <c r="B187" t="inlineStr">
@@ -14672,7 +14660,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" t="n">
         <v>186</v>
       </c>
       <c r="B188" t="inlineStr">
@@ -14748,7 +14736,7 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" t="n">
         <v>187</v>
       </c>
       <c r="B189" t="inlineStr">
@@ -14824,7 +14812,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" t="n">
         <v>188</v>
       </c>
       <c r="B190" t="inlineStr">
@@ -14900,7 +14888,7 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" t="n">
         <v>189</v>
       </c>
       <c r="B191" t="inlineStr">
@@ -14976,7 +14964,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" t="n">
         <v>190</v>
       </c>
       <c r="B192" t="inlineStr">
@@ -15052,7 +15040,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" t="n">
         <v>191</v>
       </c>
       <c r="B193" t="inlineStr">
@@ -15128,7 +15116,7 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" t="n">
         <v>192</v>
       </c>
       <c r="B194" t="inlineStr">
@@ -15204,7 +15192,7 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" t="n">
         <v>193</v>
       </c>
       <c r="B195" t="inlineStr">
@@ -15280,7 +15268,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" t="n">
         <v>194</v>
       </c>
       <c r="B196" t="inlineStr">
@@ -15356,7 +15344,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" t="n">
         <v>195</v>
       </c>
       <c r="B197" t="inlineStr">
@@ -15432,7 +15420,7 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" t="n">
         <v>196</v>
       </c>
       <c r="B198" t="inlineStr">
@@ -15508,7 +15496,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" t="n">
         <v>197</v>
       </c>
       <c r="B199" t="inlineStr">
@@ -15584,7 +15572,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" t="n">
         <v>198</v>
       </c>
       <c r="B200" t="inlineStr">
@@ -15660,7 +15648,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" t="n">
         <v>199</v>
       </c>
       <c r="B201" t="inlineStr">
@@ -15736,7 +15724,7 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" t="n">
         <v>200</v>
       </c>
       <c r="B202" t="inlineStr">
@@ -15812,7 +15800,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" t="n">
         <v>201</v>
       </c>
       <c r="B203" t="inlineStr">
@@ -15888,7 +15876,7 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" t="n">
         <v>202</v>
       </c>
       <c r="B204" t="inlineStr">
@@ -15964,7 +15952,7 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" t="n">
         <v>203</v>
       </c>
       <c r="B205" t="inlineStr">
@@ -16040,7 +16028,7 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" t="n">
         <v>204</v>
       </c>
       <c r="B206" t="inlineStr">
@@ -16116,7 +16104,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" t="n">
         <v>205</v>
       </c>
       <c r="B207" t="inlineStr">
@@ -16192,7 +16180,7 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" t="n">
         <v>206</v>
       </c>
       <c r="B208" t="inlineStr">
@@ -16268,7 +16256,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" t="n">
         <v>207</v>
       </c>
       <c r="B209" t="inlineStr">
@@ -16344,7 +16332,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" t="n">
         <v>208</v>
       </c>
       <c r="B210" t="inlineStr">
@@ -16420,7 +16408,7 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" t="n">
         <v>209</v>
       </c>
       <c r="B211" t="inlineStr">
@@ -16496,7 +16484,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" t="n">
         <v>210</v>
       </c>
       <c r="B212" t="inlineStr">
@@ -16572,7 +16560,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" t="n">
         <v>211</v>
       </c>
       <c r="B213" t="inlineStr">
@@ -16648,7 +16636,7 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" t="n">
         <v>212</v>
       </c>
       <c r="B214" t="inlineStr">
@@ -16724,7 +16712,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" t="n">
         <v>213</v>
       </c>
       <c r="B215" t="inlineStr">
@@ -16800,7 +16788,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" t="n">
         <v>214</v>
       </c>
       <c r="B216" t="inlineStr">
@@ -16876,7 +16864,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" t="n">
         <v>215</v>
       </c>
       <c r="B217" t="inlineStr">
@@ -16952,7 +16940,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" t="n">
         <v>216</v>
       </c>
       <c r="B218" t="inlineStr">
@@ -17028,7 +17016,7 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" t="n">
         <v>217</v>
       </c>
       <c r="B219" t="inlineStr">
@@ -17104,7 +17092,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" t="n">
         <v>218</v>
       </c>
       <c r="B220" t="inlineStr">
@@ -17180,7 +17168,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" t="n">
         <v>219</v>
       </c>
       <c r="B221" t="inlineStr">
@@ -17256,7 +17244,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" t="n">
         <v>220</v>
       </c>
       <c r="B222" t="inlineStr">
@@ -17332,7 +17320,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" t="n">
         <v>221</v>
       </c>
       <c r="B223" t="inlineStr">
@@ -17408,7 +17396,7 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" t="n">
         <v>222</v>
       </c>
       <c r="B224" t="inlineStr">
@@ -17484,7 +17472,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" t="n">
         <v>223</v>
       </c>
       <c r="B225" t="inlineStr">
@@ -17560,7 +17548,7 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" t="n">
         <v>224</v>
       </c>
       <c r="B226" t="inlineStr">
@@ -17636,7 +17624,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" t="n">
         <v>225</v>
       </c>
       <c r="B227" t="inlineStr">
@@ -17712,7 +17700,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" t="n">
         <v>226</v>
       </c>
       <c r="B228" t="inlineStr">
@@ -17788,7 +17776,7 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" t="n">
         <v>227</v>
       </c>
       <c r="B229" t="inlineStr">
@@ -17864,7 +17852,7 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" t="n">
         <v>228</v>
       </c>
       <c r="B230" t="inlineStr">
@@ -17940,7 +17928,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" t="n">
         <v>229</v>
       </c>
       <c r="B231" t="inlineStr">
@@ -18016,7 +18004,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" t="n">
         <v>230</v>
       </c>
       <c r="B232" t="inlineStr">
@@ -18092,7 +18080,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" t="n">
         <v>231</v>
       </c>
       <c r="B233" t="inlineStr">
@@ -18168,7 +18156,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" t="n">
         <v>232</v>
       </c>
       <c r="B234" t="inlineStr">
@@ -18244,7 +18232,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" t="n">
         <v>233</v>
       </c>
       <c r="B235" t="inlineStr">
@@ -18320,7 +18308,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" t="n">
         <v>234</v>
       </c>
       <c r="B236" t="inlineStr">
@@ -18396,7 +18384,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" t="n">
         <v>235</v>
       </c>
       <c r="B237" t="inlineStr">
@@ -18472,7 +18460,7 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" t="n">
         <v>236</v>
       </c>
       <c r="B238" t="inlineStr">
@@ -18548,7 +18536,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" t="n">
         <v>237</v>
       </c>
       <c r="B239" t="inlineStr">
@@ -18624,7 +18612,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" t="n">
         <v>238</v>
       </c>
       <c r="B240" t="inlineStr">
@@ -18700,7 +18688,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" t="n">
         <v>239</v>
       </c>
       <c r="B241" t="inlineStr">
@@ -18776,7 +18764,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" t="n">
         <v>240</v>
       </c>
       <c r="B242" t="inlineStr">
@@ -18852,7 +18840,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" t="n">
         <v>241</v>
       </c>
       <c r="B243" t="inlineStr">
@@ -18928,7 +18916,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" t="n">
         <v>242</v>
       </c>
       <c r="B244" t="inlineStr">
@@ -19004,7 +18992,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" t="n">
         <v>243</v>
       </c>
       <c r="B245" t="inlineStr">
@@ -19080,7 +19068,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" t="n">
         <v>244</v>
       </c>
       <c r="B246" t="inlineStr">
@@ -19156,7 +19144,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" t="n">
         <v>245</v>
       </c>
       <c r="B247" t="inlineStr">
@@ -19232,7 +19220,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" t="n">
         <v>246</v>
       </c>
       <c r="B248" t="inlineStr">
@@ -19308,7 +19296,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" t="n">
         <v>247</v>
       </c>
       <c r="B249" t="inlineStr">
@@ -19384,7 +19372,7 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" t="n">
         <v>248</v>
       </c>
       <c r="B250" t="inlineStr">
@@ -19460,7 +19448,7 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" s="1" t="n">
+      <c r="A251" t="n">
         <v>249</v>
       </c>
       <c r="B251" t="inlineStr">
@@ -19536,7 +19524,7 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" s="1" t="n">
+      <c r="A252" t="n">
         <v>250</v>
       </c>
       <c r="B252" t="inlineStr">
@@ -19612,7 +19600,7 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" s="1" t="n">
+      <c r="A253" t="n">
         <v>251</v>
       </c>
       <c r="B253" t="inlineStr">
@@ -19688,7 +19676,7 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="1" t="n">
+      <c r="A254" t="n">
         <v>252</v>
       </c>
       <c r="B254" t="inlineStr">
@@ -19764,7 +19752,7 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" s="1" t="n">
+      <c r="A255" t="n">
         <v>253</v>
       </c>
       <c r="B255" t="inlineStr">
@@ -19840,7 +19828,7 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" s="1" t="n">
+      <c r="A256" t="n">
         <v>254</v>
       </c>
       <c r="B256" t="inlineStr">
@@ -19916,7 +19904,7 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" s="1" t="n">
+      <c r="A257" t="n">
         <v>255</v>
       </c>
       <c r="B257" t="inlineStr">
@@ -19992,7 +19980,7 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" s="1" t="n">
+      <c r="A258" t="n">
         <v>256</v>
       </c>
       <c r="B258" t="inlineStr">
@@ -20068,7 +20056,7 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" s="1" t="n">
+      <c r="A259" t="n">
         <v>257</v>
       </c>
       <c r="B259" t="inlineStr">
@@ -20144,7 +20132,7 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="1" t="n">
+      <c r="A260" t="n">
         <v>258</v>
       </c>
       <c r="B260" t="inlineStr">
@@ -20220,7 +20208,7 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" s="1" t="n">
+      <c r="A261" t="n">
         <v>259</v>
       </c>
       <c r="B261" t="inlineStr">
@@ -20296,7 +20284,7 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" s="1" t="n">
+      <c r="A262" t="n">
         <v>260</v>
       </c>
       <c r="B262" t="inlineStr">
@@ -20372,7 +20360,7 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="1" t="n">
+      <c r="A263" t="n">
         <v>261</v>
       </c>
       <c r="B263" t="inlineStr">
@@ -20448,7 +20436,7 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" s="1" t="n">
+      <c r="A264" t="n">
         <v>262</v>
       </c>
       <c r="B264" t="inlineStr">
@@ -20524,7 +20512,7 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" s="1" t="n">
+      <c r="A265" t="n">
         <v>263</v>
       </c>
       <c r="B265" t="inlineStr">
@@ -20600,7 +20588,7 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" s="1" t="n">
+      <c r="A266" t="n">
         <v>264</v>
       </c>
       <c r="B266" t="inlineStr">
@@ -20676,7 +20664,7 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" s="1" t="n">
+      <c r="A267" t="n">
         <v>265</v>
       </c>
       <c r="B267" t="inlineStr">
@@ -20752,7 +20740,7 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" s="1" t="n">
+      <c r="A268" t="n">
         <v>266</v>
       </c>
       <c r="B268" t="inlineStr">
@@ -20828,7 +20816,7 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" s="1" t="n">
+      <c r="A269" t="n">
         <v>267</v>
       </c>
       <c r="B269" t="inlineStr">
@@ -20904,7 +20892,7 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" s="1" t="n">
+      <c r="A270" t="n">
         <v>268</v>
       </c>
       <c r="B270" t="inlineStr">
@@ -20980,7 +20968,7 @@
       </c>
     </row>
     <row r="271">
-      <c r="A271" s="1" t="n">
+      <c r="A271" t="n">
         <v>269</v>
       </c>
       <c r="B271" t="inlineStr">
@@ -21056,7 +21044,7 @@
       </c>
     </row>
     <row r="272">
-      <c r="A272" s="1" t="n">
+      <c r="A272" t="n">
         <v>270</v>
       </c>
       <c r="B272" t="inlineStr">
@@ -21132,7 +21120,7 @@
       </c>
     </row>
     <row r="273">
-      <c r="A273" s="1" t="n">
+      <c r="A273" t="n">
         <v>271</v>
       </c>
       <c r="B273" t="inlineStr">
@@ -21208,7 +21196,7 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="1" t="n">
+      <c r="A274" t="n">
         <v>272</v>
       </c>
       <c r="B274" t="inlineStr">
@@ -21284,7 +21272,7 @@
       </c>
     </row>
     <row r="275">
-      <c r="A275" s="1" t="n">
+      <c r="A275" t="n">
         <v>273</v>
       </c>
       <c r="B275" t="inlineStr">
@@ -21360,7 +21348,7 @@
       </c>
     </row>
     <row r="276">
-      <c r="A276" s="1" t="n">
+      <c r="A276" t="n">
         <v>274</v>
       </c>
       <c r="B276" t="inlineStr">
@@ -21436,7 +21424,7 @@
       </c>
     </row>
     <row r="277">
-      <c r="A277" s="1" t="n">
+      <c r="A277" t="n">
         <v>275</v>
       </c>
       <c r="B277" t="inlineStr">
@@ -21512,7 +21500,7 @@
       </c>
     </row>
     <row r="278">
-      <c r="A278" s="1" t="n">
+      <c r="A278" t="n">
         <v>276</v>
       </c>
       <c r="B278" t="inlineStr">
@@ -21588,7 +21576,7 @@
       </c>
     </row>
     <row r="279">
-      <c r="A279" s="1" t="n">
+      <c r="A279" t="n">
         <v>277</v>
       </c>
       <c r="B279" t="inlineStr">
@@ -21664,7 +21652,7 @@
       </c>
     </row>
     <row r="280">
-      <c r="A280" s="1" t="n">
+      <c r="A280" t="n">
         <v>278</v>
       </c>
       <c r="B280" t="inlineStr">
@@ -21740,7 +21728,7 @@
       </c>
     </row>
     <row r="281">
-      <c r="A281" s="1" t="n">
+      <c r="A281" t="n">
         <v>279</v>
       </c>
       <c r="B281" t="inlineStr">
@@ -21816,7 +21804,7 @@
       </c>
     </row>
     <row r="282">
-      <c r="A282" s="1" t="n">
+      <c r="A282" t="n">
         <v>280</v>
       </c>
       <c r="B282" t="inlineStr">
@@ -21892,7 +21880,7 @@
       </c>
     </row>
     <row r="283">
-      <c r="A283" s="1" t="n">
+      <c r="A283" t="n">
         <v>281</v>
       </c>
       <c r="B283" t="inlineStr">
@@ -21968,7 +21956,7 @@
       </c>
     </row>
     <row r="284">
-      <c r="A284" s="1" t="n">
+      <c r="A284" t="n">
         <v>282</v>
       </c>
       <c r="B284" t="inlineStr">
@@ -22044,7 +22032,7 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="1" t="n">
+      <c r="A285" t="n">
         <v>283</v>
       </c>
       <c r="B285" t="inlineStr">
@@ -22120,7 +22108,7 @@
       </c>
     </row>
     <row r="286">
-      <c r="A286" s="1" t="n">
+      <c r="A286" t="n">
         <v>284</v>
       </c>
       <c r="B286" t="inlineStr">
@@ -22196,7 +22184,7 @@
       </c>
     </row>
     <row r="287">
-      <c r="A287" s="1" t="n">
+      <c r="A287" t="n">
         <v>285</v>
       </c>
       <c r="B287" t="inlineStr">
@@ -22272,7 +22260,7 @@
       </c>
     </row>
     <row r="288">
-      <c r="A288" s="1" t="n">
+      <c r="A288" t="n">
         <v>286</v>
       </c>
       <c r="B288" t="inlineStr">
@@ -22348,7 +22336,7 @@
       </c>
     </row>
     <row r="289">
-      <c r="A289" s="1" t="n">
+      <c r="A289" t="n">
         <v>287</v>
       </c>
       <c r="B289" t="inlineStr">
@@ -22424,7 +22412,7 @@
       </c>
     </row>
     <row r="290">
-      <c r="A290" s="1" t="n">
+      <c r="A290" t="n">
         <v>288</v>
       </c>
       <c r="B290" t="inlineStr">
@@ -22500,7 +22488,7 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="1" t="n">
+      <c r="A291" t="n">
         <v>289</v>
       </c>
       <c r="B291" t="inlineStr">
@@ -22576,7 +22564,7 @@
       </c>
     </row>
     <row r="292">
-      <c r="A292" s="1" t="n">
+      <c r="A292" t="n">
         <v>290</v>
       </c>
       <c r="B292" t="inlineStr">
@@ -22652,7 +22640,7 @@
       </c>
     </row>
     <row r="293">
-      <c r="A293" s="1" t="n">
+      <c r="A293" t="n">
         <v>291</v>
       </c>
       <c r="B293" t="inlineStr">
@@ -22728,7 +22716,7 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="1" t="n">
+      <c r="A294" t="n">
         <v>292</v>
       </c>
       <c r="B294" t="inlineStr">
@@ -22804,7 +22792,7 @@
       </c>
     </row>
     <row r="295">
-      <c r="A295" s="1" t="n">
+      <c r="A295" t="n">
         <v>293</v>
       </c>
       <c r="B295" t="inlineStr">
@@ -22880,7 +22868,7 @@
       </c>
     </row>
     <row r="296">
-      <c r="A296" s="1" t="n">
+      <c r="A296" t="n">
         <v>294</v>
       </c>
       <c r="B296" t="inlineStr">
@@ -22956,7 +22944,7 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="1" t="n">
+      <c r="A297" t="n">
         <v>295</v>
       </c>
       <c r="B297" t="inlineStr">
@@ -23032,7 +23020,7 @@
       </c>
     </row>
     <row r="298">
-      <c r="A298" s="1" t="n">
+      <c r="A298" t="n">
         <v>296</v>
       </c>
       <c r="B298" t="inlineStr">
@@ -23108,7 +23096,7 @@
       </c>
     </row>
     <row r="299">
-      <c r="A299" s="1" t="n">
+      <c r="A299" t="n">
         <v>297</v>
       </c>
       <c r="B299" t="inlineStr">
@@ -23184,7 +23172,7 @@
       </c>
     </row>
     <row r="300">
-      <c r="A300" s="1" t="n">
+      <c r="A300" t="n">
         <v>298</v>
       </c>
       <c r="B300" t="inlineStr">
@@ -23260,7 +23248,7 @@
       </c>
     </row>
     <row r="301">
-      <c r="A301" s="1" t="n">
+      <c r="A301" t="n">
         <v>299</v>
       </c>
       <c r="B301" t="inlineStr">
@@ -23336,7 +23324,7 @@
       </c>
     </row>
     <row r="302">
-      <c r="A302" s="1" t="n">
+      <c r="A302" t="n">
         <v>300</v>
       </c>
       <c r="B302" t="inlineStr">
@@ -23412,7 +23400,7 @@
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="1" t="n">
+      <c r="A303" t="n">
         <v>301</v>
       </c>
       <c r="B303" t="inlineStr">
@@ -23488,7 +23476,7 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="1" t="n">
+      <c r="A304" t="n">
         <v>302</v>
       </c>
       <c r="B304" t="inlineStr">
@@ -23564,7 +23552,7 @@
       </c>
     </row>
     <row r="305">
-      <c r="A305" s="1" t="n">
+      <c r="A305" t="n">
         <v>303</v>
       </c>
       <c r="B305" t="inlineStr">
@@ -23640,7 +23628,7 @@
       </c>
     </row>
     <row r="306">
-      <c r="A306" s="1" t="n">
+      <c r="A306" t="n">
         <v>304</v>
       </c>
       <c r="B306" t="inlineStr">
@@ -23716,7 +23704,7 @@
       </c>
     </row>
     <row r="307">
-      <c r="A307" s="1" t="n">
+      <c r="A307" t="n">
         <v>305</v>
       </c>
       <c r="B307" t="inlineStr">
@@ -23792,7 +23780,7 @@
       </c>
     </row>
     <row r="308">
-      <c r="A308" s="1" t="n">
+      <c r="A308" t="n">
         <v>306</v>
       </c>
       <c r="B308" t="inlineStr">
@@ -23868,7 +23856,7 @@
       </c>
     </row>
     <row r="309">
-      <c r="A309" s="1" t="n">
+      <c r="A309" t="n">
         <v>307</v>
       </c>
       <c r="B309" t="inlineStr">
@@ -23944,7 +23932,7 @@
       </c>
     </row>
     <row r="310">
-      <c r="A310" s="1" t="n">
+      <c r="A310" t="n">
         <v>308</v>
       </c>
       <c r="B310" t="inlineStr">
@@ -24020,7 +24008,7 @@
       </c>
     </row>
     <row r="311">
-      <c r="A311" s="1" t="n">
+      <c r="A311" t="n">
         <v>309</v>
       </c>
       <c r="B311" t="inlineStr">
@@ -24096,7 +24084,7 @@
       </c>
     </row>
     <row r="312">
-      <c r="A312" s="1" t="n">
+      <c r="A312" t="n">
         <v>310</v>
       </c>
       <c r="B312" t="inlineStr">
@@ -24172,7 +24160,7 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="1" t="n">
+      <c r="A313" t="n">
         <v>311</v>
       </c>
       <c r="B313" t="inlineStr">
@@ -24248,7 +24236,7 @@
       </c>
     </row>
     <row r="314">
-      <c r="A314" s="1" t="n">
+      <c r="A314" t="n">
         <v>312</v>
       </c>
       <c r="B314" t="inlineStr">
@@ -24324,7 +24312,7 @@
       </c>
     </row>
     <row r="315">
-      <c r="A315" s="1" t="n">
+      <c r="A315" t="n">
         <v>313</v>
       </c>
       <c r="B315" t="inlineStr">
@@ -24400,7 +24388,7 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="1" t="n">
+      <c r="A316" t="n">
         <v>314</v>
       </c>
       <c r="B316" t="inlineStr">
@@ -24476,7 +24464,7 @@
       </c>
     </row>
     <row r="317">
-      <c r="A317" s="1" t="n">
+      <c r="A317" t="n">
         <v>315</v>
       </c>
       <c r="B317" t="inlineStr">
@@ -24552,7 +24540,7 @@
       </c>
     </row>
     <row r="318">
-      <c r="A318" s="1" t="n">
+      <c r="A318" t="n">
         <v>316</v>
       </c>
       <c r="B318" t="inlineStr">
@@ -24628,7 +24616,7 @@
       </c>
     </row>
     <row r="319">
-      <c r="A319" s="1" t="n">
+      <c r="A319" t="n">
         <v>317</v>
       </c>
       <c r="B319" t="inlineStr">
@@ -24704,7 +24692,7 @@
       </c>
     </row>
     <row r="320">
-      <c r="A320" s="1" t="n">
+      <c r="A320" t="n">
         <v>318</v>
       </c>
       <c r="B320" t="inlineStr">
@@ -24780,7 +24768,7 @@
       </c>
     </row>
     <row r="321">
-      <c r="A321" s="1" t="n">
+      <c r="A321" t="n">
         <v>319</v>
       </c>
       <c r="B321" t="inlineStr">
@@ -24856,7 +24844,7 @@
       </c>
     </row>
     <row r="322">
-      <c r="A322" s="1" t="n">
+      <c r="A322" t="n">
         <v>320</v>
       </c>
       <c r="B322" t="inlineStr">
@@ -24932,7 +24920,7 @@
       </c>
     </row>
     <row r="323">
-      <c r="A323" s="1" t="n">
+      <c r="A323" t="n">
         <v>321</v>
       </c>
       <c r="B323" t="inlineStr">
@@ -25008,7 +24996,7 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="1" t="n">
+      <c r="A324" t="n">
         <v>322</v>
       </c>
       <c r="B324" t="inlineStr">
@@ -25084,7 +25072,7 @@
       </c>
     </row>
     <row r="325">
-      <c r="A325" s="1" t="n">
+      <c r="A325" t="n">
         <v>323</v>
       </c>
       <c r="B325" t="inlineStr">
@@ -25160,7 +25148,7 @@
       </c>
     </row>
     <row r="326">
-      <c r="A326" s="1" t="n">
+      <c r="A326" t="n">
         <v>324</v>
       </c>
       <c r="B326" t="inlineStr">
@@ -25236,7 +25224,7 @@
       </c>
     </row>
     <row r="327">
-      <c r="A327" s="1" t="n">
+      <c r="A327" t="n">
         <v>325</v>
       </c>
       <c r="B327" t="inlineStr">
@@ -25312,7 +25300,7 @@
       </c>
     </row>
     <row r="328">
-      <c r="A328" s="1" t="n">
+      <c r="A328" t="n">
         <v>326</v>
       </c>
       <c r="B328" t="inlineStr">
@@ -25388,7 +25376,7 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="1" t="n">
+      <c r="A329" t="n">
         <v>327</v>
       </c>
       <c r="B329" t="inlineStr">
@@ -25464,7 +25452,7 @@
       </c>
     </row>
     <row r="330">
-      <c r="A330" s="1" t="n">
+      <c r="A330" t="n">
         <v>328</v>
       </c>
       <c r="B330" t="inlineStr">
@@ -25540,7 +25528,7 @@
       </c>
     </row>
     <row r="331">
-      <c r="A331" s="1" t="n">
+      <c r="A331" t="n">
         <v>329</v>
       </c>
       <c r="B331" t="inlineStr">
@@ -25616,7 +25604,7 @@
       </c>
     </row>
     <row r="332">
-      <c r="A332" s="1" t="n">
+      <c r="A332" t="n">
         <v>330</v>
       </c>
       <c r="B332" t="inlineStr">
@@ -25692,7 +25680,7 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="1" t="n">
+      <c r="A333" t="n">
         <v>331</v>
       </c>
       <c r="B333" t="inlineStr">
@@ -25768,7 +25756,7 @@
       </c>
     </row>
     <row r="334">
-      <c r="A334" s="1" t="n">
+      <c r="A334" t="n">
         <v>332</v>
       </c>
       <c r="B334" t="inlineStr">
@@ -25844,7 +25832,7 @@
       </c>
     </row>
     <row r="335">
-      <c r="A335" s="1" t="n">
+      <c r="A335" t="n">
         <v>333</v>
       </c>
       <c r="B335" t="inlineStr">
@@ -25920,7 +25908,7 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="1" t="n">
+      <c r="A336" t="n">
         <v>334</v>
       </c>
       <c r="B336" t="inlineStr">
@@ -25996,7 +25984,7 @@
       </c>
     </row>
     <row r="337">
-      <c r="A337" s="1" t="n">
+      <c r="A337" t="n">
         <v>335</v>
       </c>
       <c r="B337" t="inlineStr">
@@ -26072,7 +26060,7 @@
       </c>
     </row>
     <row r="338">
-      <c r="A338" s="1" t="n">
+      <c r="A338" t="n">
         <v>336</v>
       </c>
       <c r="B338" t="inlineStr">
@@ -26148,7 +26136,7 @@
       </c>
     </row>
     <row r="339">
-      <c r="A339" s="1" t="n">
+      <c r="A339" t="n">
         <v>337</v>
       </c>
       <c r="B339" t="inlineStr">
@@ -26224,7 +26212,7 @@
       </c>
     </row>
     <row r="340">
-      <c r="A340" s="1" t="n">
+      <c r="A340" t="n">
         <v>338</v>
       </c>
       <c r="B340" t="inlineStr">
@@ -26300,7 +26288,7 @@
       </c>
     </row>
     <row r="341">
-      <c r="A341" s="1" t="n">
+      <c r="A341" t="n">
         <v>339</v>
       </c>
       <c r="B341" t="inlineStr">
@@ -26376,7 +26364,7 @@
       </c>
     </row>
     <row r="342">
-      <c r="A342" s="1" t="n">
+      <c r="A342" t="n">
         <v>340</v>
       </c>
       <c r="B342" t="inlineStr">
@@ -26452,7 +26440,7 @@
       </c>
     </row>
     <row r="343">
-      <c r="A343" s="1" t="n">
+      <c r="A343" t="n">
         <v>341</v>
       </c>
       <c r="B343" t="inlineStr">
@@ -26528,7 +26516,7 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="1" t="n">
+      <c r="A344" t="n">
         <v>342</v>
       </c>
       <c r="B344" t="inlineStr">
@@ -26604,7 +26592,7 @@
       </c>
     </row>
     <row r="345">
-      <c r="A345" s="1" t="n">
+      <c r="A345" t="n">
         <v>343</v>
       </c>
       <c r="B345" t="inlineStr">
@@ -26680,7 +26668,7 @@
       </c>
     </row>
     <row r="346">
-      <c r="A346" s="1" t="n">
+      <c r="A346" t="n">
         <v>344</v>
       </c>
       <c r="B346" t="inlineStr">
@@ -26756,7 +26744,7 @@
       </c>
     </row>
     <row r="347">
-      <c r="A347" s="1" t="n">
+      <c r="A347" t="n">
         <v>345</v>
       </c>
       <c r="B347" t="inlineStr">
@@ -26832,7 +26820,7 @@
       </c>
     </row>
     <row r="348">
-      <c r="A348" s="1" t="n">
+      <c r="A348" t="n">
         <v>346</v>
       </c>
       <c r="B348" t="inlineStr">
@@ -26908,7 +26896,7 @@
       </c>
     </row>
     <row r="349">
-      <c r="A349" s="1" t="n">
+      <c r="A349" t="n">
         <v>347</v>
       </c>
       <c r="B349" t="inlineStr">
@@ -26984,7 +26972,7 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="1" t="n">
+      <c r="A350" t="n">
         <v>348</v>
       </c>
       <c r="B350" t="inlineStr">
@@ -27060,7 +27048,7 @@
       </c>
     </row>
     <row r="351">
-      <c r="A351" s="1" t="n">
+      <c r="A351" t="n">
         <v>349</v>
       </c>
       <c r="B351" t="inlineStr">
@@ -27136,7 +27124,7 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="1" t="n">
+      <c r="A352" t="n">
         <v>350</v>
       </c>
       <c r="B352" t="inlineStr">
@@ -27212,7 +27200,7 @@
       </c>
     </row>
     <row r="353">
-      <c r="A353" s="1" t="n">
+      <c r="A353" t="n">
         <v>351</v>
       </c>
       <c r="B353" t="inlineStr">
@@ -27288,7 +27276,7 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="1" t="n">
+      <c r="A354" t="n">
         <v>352</v>
       </c>
       <c r="B354" t="inlineStr">
@@ -27364,7 +27352,7 @@
       </c>
     </row>
     <row r="355">
-      <c r="A355" s="1" t="n">
+      <c r="A355" t="n">
         <v>353</v>
       </c>
       <c r="B355" t="inlineStr">
@@ -27440,7 +27428,7 @@
       </c>
     </row>
     <row r="356">
-      <c r="A356" s="1" t="n">
+      <c r="A356" t="n">
         <v>354</v>
       </c>
       <c r="B356" t="inlineStr">
@@ -27516,7 +27504,7 @@
       </c>
     </row>
     <row r="357">
-      <c r="A357" s="1" t="n">
+      <c r="A357" t="n">
         <v>355</v>
       </c>
       <c r="B357" t="inlineStr">
@@ -27592,7 +27580,7 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="1" t="n">
+      <c r="A358" t="n">
         <v>356</v>
       </c>
       <c r="B358" t="inlineStr">
@@ -27668,7 +27656,7 @@
       </c>
     </row>
     <row r="359">
-      <c r="A359" s="1" t="n">
+      <c r="A359" t="n">
         <v>357</v>
       </c>
       <c r="B359" t="inlineStr">
@@ -27744,7 +27732,7 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="1" t="n">
+      <c r="A360" t="n">
         <v>358</v>
       </c>
       <c r="B360" t="inlineStr">
@@ -27820,7 +27808,7 @@
       </c>
     </row>
     <row r="361">
-      <c r="A361" s="1" t="n">
+      <c r="A361" t="n">
         <v>359</v>
       </c>
       <c r="B361" t="inlineStr">
@@ -27896,7 +27884,7 @@
       </c>
     </row>
     <row r="362">
-      <c r="A362" s="1" t="n">
+      <c r="A362" t="n">
         <v>360</v>
       </c>
       <c r="B362" t="inlineStr">
@@ -27972,7 +27960,7 @@
       </c>
     </row>
     <row r="363">
-      <c r="A363" s="1" t="n">
+      <c r="A363" t="n">
         <v>361</v>
       </c>
       <c r="B363" t="inlineStr">
@@ -28048,7 +28036,7 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="1" t="n">
+      <c r="A364" t="n">
         <v>362</v>
       </c>
       <c r="B364" t="inlineStr">
@@ -28124,7 +28112,7 @@
       </c>
     </row>
     <row r="365">
-      <c r="A365" s="1" t="n">
+      <c r="A365" t="n">
         <v>363</v>
       </c>
       <c r="B365" t="inlineStr">
@@ -28200,7 +28188,7 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="1" t="n">
+      <c r="A366" t="n">
         <v>364</v>
       </c>
       <c r="B366" t="inlineStr">
@@ -28276,7 +28264,7 @@
       </c>
     </row>
     <row r="367">
-      <c r="A367" s="1" t="n">
+      <c r="A367" t="n">
         <v>365</v>
       </c>
       <c r="B367" t="inlineStr">
@@ -28352,7 +28340,7 @@
       </c>
     </row>
     <row r="368">
-      <c r="A368" s="1" t="n">
+      <c r="A368" t="n">
         <v>366</v>
       </c>
       <c r="B368" t="inlineStr">
@@ -28428,7 +28416,7 @@
       </c>
     </row>
     <row r="369">
-      <c r="A369" s="1" t="n">
+      <c r="A369" t="n">
         <v>367</v>
       </c>
       <c r="B369" t="inlineStr">
@@ -28504,7 +28492,7 @@
       </c>
     </row>
     <row r="370">
-      <c r="A370" s="1" t="n">
+      <c r="A370" t="n">
         <v>368</v>
       </c>
       <c r="B370" t="inlineStr">
@@ -28580,7 +28568,7 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="1" t="n">
+      <c r="A371" t="n">
         <v>369</v>
       </c>
       <c r="B371" t="inlineStr">
@@ -28656,7 +28644,7 @@
       </c>
     </row>
     <row r="372">
-      <c r="A372" s="1" t="n">
+      <c r="A372" t="n">
         <v>370</v>
       </c>
       <c r="B372" t="inlineStr">
@@ -28732,7 +28720,7 @@
       </c>
     </row>
     <row r="373">
-      <c r="A373" s="1" t="n">
+      <c r="A373" t="n">
         <v>371</v>
       </c>
       <c r="B373" t="inlineStr">
@@ -28808,7 +28796,7 @@
       </c>
     </row>
     <row r="374">
-      <c r="A374" s="1" t="n">
+      <c r="A374" t="n">
         <v>372</v>
       </c>
       <c r="B374" t="inlineStr">
@@ -28884,7 +28872,7 @@
       </c>
     </row>
     <row r="375">
-      <c r="A375" s="1" t="n">
+      <c r="A375" t="n">
         <v>373</v>
       </c>
       <c r="B375" t="inlineStr">
@@ -28960,7 +28948,7 @@
       </c>
     </row>
     <row r="376">
-      <c r="A376" s="1" t="n">
+      <c r="A376" t="n">
         <v>374</v>
       </c>
       <c r="B376" t="inlineStr">
@@ -29036,7 +29024,7 @@
       </c>
     </row>
     <row r="377">
-      <c r="A377" s="1" t="n">
+      <c r="A377" t="n">
         <v>375</v>
       </c>
       <c r="B377" t="inlineStr">
@@ -29112,7 +29100,7 @@
       </c>
     </row>
     <row r="378">
-      <c r="A378" s="1" t="n">
+      <c r="A378" t="n">
         <v>376</v>
       </c>
       <c r="B378" t="inlineStr">
@@ -29188,7 +29176,7 @@
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="1" t="n">
+      <c r="A379" t="n">
         <v>377</v>
       </c>
       <c r="B379" t="inlineStr">
@@ -29264,7 +29252,7 @@
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="1" t="n">
+      <c r="A380" t="n">
         <v>378</v>
       </c>
       <c r="B380" t="inlineStr">
@@ -29340,7 +29328,7 @@
       </c>
     </row>
     <row r="381">
-      <c r="A381" s="1" t="n">
+      <c r="A381" t="n">
         <v>379</v>
       </c>
       <c r="B381" t="inlineStr">
@@ -29416,7 +29404,7 @@
       </c>
     </row>
     <row r="382">
-      <c r="A382" s="1" t="n">
+      <c r="A382" t="n">
         <v>380</v>
       </c>
       <c r="B382" t="inlineStr">
@@ -29492,7 +29480,7 @@
       </c>
     </row>
     <row r="383">
-      <c r="A383" s="1" t="n">
+      <c r="A383" t="n">
         <v>381</v>
       </c>
       <c r="B383" t="inlineStr">
@@ -29568,7 +29556,7 @@
       </c>
     </row>
     <row r="384">
-      <c r="A384" s="1" t="n">
+      <c r="A384" t="n">
         <v>382</v>
       </c>
       <c r="B384" t="inlineStr">
@@ -29644,7 +29632,7 @@
       </c>
     </row>
     <row r="385">
-      <c r="A385" s="1" t="n">
+      <c r="A385" t="n">
         <v>383</v>
       </c>
       <c r="B385" t="inlineStr">
@@ -29720,7 +29708,7 @@
       </c>
     </row>
     <row r="386">
-      <c r="A386" s="1" t="n">
+      <c r="A386" t="n">
         <v>384</v>
       </c>
       <c r="B386" t="inlineStr">
@@ -29796,7 +29784,7 @@
       </c>
     </row>
     <row r="387">
-      <c r="A387" s="1" t="n">
+      <c r="A387" t="n">
         <v>385</v>
       </c>
       <c r="B387" t="inlineStr">
@@ -29872,7 +29860,7 @@
       </c>
     </row>
     <row r="388">
-      <c r="A388" s="1" t="n">
+      <c r="A388" t="n">
         <v>386</v>
       </c>
       <c r="B388" t="inlineStr">
@@ -29948,7 +29936,7 @@
       </c>
     </row>
     <row r="389">
-      <c r="A389" s="1" t="n">
+      <c r="A389" t="n">
         <v>387</v>
       </c>
       <c r="B389" t="inlineStr">
@@ -30024,7 +30012,7 @@
       </c>
     </row>
     <row r="390">
-      <c r="A390" s="1" t="n">
+      <c r="A390" t="n">
         <v>388</v>
       </c>
       <c r="B390" t="inlineStr">
@@ -30100,7 +30088,7 @@
       </c>
     </row>
     <row r="391">
-      <c r="A391" s="1" t="n">
+      <c r="A391" t="n">
         <v>389</v>
       </c>
       <c r="B391" t="inlineStr">
@@ -30176,7 +30164,7 @@
       </c>
     </row>
     <row r="392">
-      <c r="A392" s="1" t="n">
+      <c r="A392" t="n">
         <v>390</v>
       </c>
       <c r="B392" t="inlineStr">
@@ -30252,7 +30240,7 @@
       </c>
     </row>
     <row r="393">
-      <c r="A393" s="1" t="n">
+      <c r="A393" t="n">
         <v>391</v>
       </c>
       <c r="B393" t="inlineStr">
@@ -30328,7 +30316,7 @@
       </c>
     </row>
     <row r="394">
-      <c r="A394" s="1" t="n">
+      <c r="A394" t="n">
         <v>392</v>
       </c>
       <c r="B394" t="inlineStr">
@@ -30404,7 +30392,7 @@
       </c>
     </row>
     <row r="395">
-      <c r="A395" s="1" t="n">
+      <c r="A395" t="n">
         <v>393</v>
       </c>
       <c r="B395" t="inlineStr">
@@ -30480,7 +30468,7 @@
       </c>
     </row>
     <row r="396">
-      <c r="A396" s="1" t="n">
+      <c r="A396" t="n">
         <v>394</v>
       </c>
       <c r="B396" t="inlineStr">
@@ -30556,7 +30544,7 @@
       </c>
     </row>
     <row r="397">
-      <c r="A397" s="1" t="n">
+      <c r="A397" t="n">
         <v>395</v>
       </c>
       <c r="B397" t="inlineStr">
@@ -30632,7 +30620,7 @@
       </c>
     </row>
     <row r="398">
-      <c r="A398" s="1" t="n">
+      <c r="A398" t="n">
         <v>396</v>
       </c>
       <c r="B398" t="inlineStr">
@@ -30708,7 +30696,7 @@
       </c>
     </row>
     <row r="399">
-      <c r="A399" s="1" t="n">
+      <c r="A399" t="n">
         <v>397</v>
       </c>
       <c r="B399" t="inlineStr">
@@ -30784,7 +30772,7 @@
       </c>
     </row>
     <row r="400">
-      <c r="A400" s="1" t="n">
+      <c r="A400" t="n">
         <v>398</v>
       </c>
       <c r="B400" t="inlineStr">
@@ -30860,7 +30848,7 @@
       </c>
     </row>
     <row r="401">
-      <c r="A401" s="1" t="n">
+      <c r="A401" t="n">
         <v>399</v>
       </c>
       <c r="B401" t="inlineStr">
@@ -30936,7 +30924,7 @@
       </c>
     </row>
     <row r="402">
-      <c r="A402" s="1" t="n">
+      <c r="A402" t="n">
         <v>400</v>
       </c>
       <c r="B402" t="inlineStr">
@@ -31012,7 +31000,7 @@
       </c>
     </row>
     <row r="403">
-      <c r="A403" s="1" t="n">
+      <c r="A403" t="n">
         <v>401</v>
       </c>
       <c r="B403" t="inlineStr">
@@ -31088,7 +31076,7 @@
       </c>
     </row>
     <row r="404">
-      <c r="A404" s="1" t="n">
+      <c r="A404" t="n">
         <v>402</v>
       </c>
       <c r="B404" t="inlineStr">
@@ -31164,7 +31152,7 @@
       </c>
     </row>
     <row r="405">
-      <c r="A405" s="1" t="n">
+      <c r="A405" t="n">
         <v>403</v>
       </c>
       <c r="B405" t="inlineStr">
@@ -31240,7 +31228,7 @@
       </c>
     </row>
     <row r="406">
-      <c r="A406" s="1" t="n">
+      <c r="A406" t="n">
         <v>404</v>
       </c>
       <c r="B406" t="inlineStr">
@@ -31316,7 +31304,7 @@
       </c>
     </row>
     <row r="407">
-      <c r="A407" s="1" t="n">
+      <c r="A407" t="n">
         <v>405</v>
       </c>
       <c r="B407" t="inlineStr">
@@ -31392,7 +31380,7 @@
       </c>
     </row>
     <row r="408">
-      <c r="A408" s="1" t="n">
+      <c r="A408" t="n">
         <v>406</v>
       </c>
       <c r="B408" t="inlineStr">
@@ -31468,7 +31456,7 @@
       </c>
     </row>
     <row r="409">
-      <c r="A409" s="1" t="n">
+      <c r="A409" t="n">
         <v>407</v>
       </c>
       <c r="B409" t="inlineStr">
@@ -31544,7 +31532,7 @@
       </c>
     </row>
     <row r="410">
-      <c r="A410" s="1" t="n">
+      <c r="A410" t="n">
         <v>408</v>
       </c>
       <c r="B410" t="inlineStr">
@@ -31620,7 +31608,7 @@
       </c>
     </row>
     <row r="411">
-      <c r="A411" s="1" t="n">
+      <c r="A411" t="n">
         <v>409</v>
       </c>
       <c r="B411" t="inlineStr">
@@ -31696,7 +31684,7 @@
       </c>
     </row>
     <row r="412">
-      <c r="A412" s="1" t="n">
+      <c r="A412" t="n">
         <v>410</v>
       </c>
       <c r="B412" t="inlineStr">
@@ -31772,7 +31760,7 @@
       </c>
     </row>
     <row r="413">
-      <c r="A413" s="1" t="n">
+      <c r="A413" t="n">
         <v>411</v>
       </c>
       <c r="B413" t="inlineStr">
@@ -31848,7 +31836,7 @@
       </c>
     </row>
     <row r="414">
-      <c r="A414" s="1" t="n">
+      <c r="A414" t="n">
         <v>412</v>
       </c>
       <c r="B414" t="inlineStr">
@@ -31924,7 +31912,7 @@
       </c>
     </row>
     <row r="415">
-      <c r="A415" s="1" t="n">
+      <c r="A415" t="n">
         <v>413</v>
       </c>
       <c r="B415" t="inlineStr">
@@ -32000,7 +31988,7 @@
       </c>
     </row>
     <row r="416">
-      <c r="A416" s="1" t="n">
+      <c r="A416" t="n">
         <v>414</v>
       </c>
       <c r="B416" t="inlineStr">
@@ -32076,7 +32064,7 @@
       </c>
     </row>
     <row r="417">
-      <c r="A417" s="1" t="n">
+      <c r="A417" t="n">
         <v>415</v>
       </c>
       <c r="B417" t="inlineStr">
@@ -32152,7 +32140,7 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="n">
+      <c r="A418" t="n">
         <v>416</v>
       </c>
       <c r="B418" t="inlineStr">
@@ -32228,7 +32216,7 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="n">
+      <c r="A419" t="n">
         <v>417</v>
       </c>
       <c r="B419" t="inlineStr">
@@ -32304,7 +32292,7 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="n">
+      <c r="A420" t="n">
         <v>418</v>
       </c>
       <c r="B420" t="inlineStr">
@@ -32380,7 +32368,7 @@
       </c>
     </row>
     <row r="421">
-      <c r="A421" s="1" t="n">
+      <c r="A421" t="n">
         <v>419</v>
       </c>
       <c r="B421" t="inlineStr">
@@ -32456,7 +32444,7 @@
       </c>
     </row>
     <row r="422">
-      <c r="A422" s="1" t="n">
+      <c r="A422" t="n">
         <v>420</v>
       </c>
       <c r="B422" t="inlineStr">
@@ -32532,7 +32520,7 @@
       </c>
     </row>
     <row r="423">
-      <c r="A423" s="1" t="n">
+      <c r="A423" t="n">
         <v>421</v>
       </c>
       <c r="B423" t="inlineStr">
@@ -32608,7 +32596,7 @@
       </c>
     </row>
     <row r="424">
-      <c r="A424" s="1" t="n">
+      <c r="A424" t="n">
         <v>422</v>
       </c>
       <c r="B424" t="inlineStr">
@@ -32684,7 +32672,7 @@
       </c>
     </row>
     <row r="425">
-      <c r="A425" s="1" t="n">
+      <c r="A425" t="n">
         <v>423</v>
       </c>
       <c r="B425" t="inlineStr">
@@ -32760,7 +32748,7 @@
       </c>
     </row>
     <row r="426">
-      <c r="A426" s="1" t="n">
+      <c r="A426" t="n">
         <v>424</v>
       </c>
       <c r="B426" t="inlineStr">
@@ -32836,7 +32824,7 @@
       </c>
     </row>
     <row r="427">
-      <c r="A427" s="1" t="n">
+      <c r="A427" t="n">
         <v>425</v>
       </c>
       <c r="B427" t="inlineStr">
@@ -32912,7 +32900,7 @@
       </c>
     </row>
     <row r="428">
-      <c r="A428" s="1" t="n">
+      <c r="A428" t="n">
         <v>426</v>
       </c>
       <c r="B428" t="inlineStr">
@@ -32988,7 +32976,7 @@
       </c>
     </row>
     <row r="429">
-      <c r="A429" s="1" t="n">
+      <c r="A429" t="n">
         <v>427</v>
       </c>
       <c r="B429" t="inlineStr">
@@ -33064,7 +33052,7 @@
       </c>
     </row>
     <row r="430">
-      <c r="A430" s="1" t="n">
+      <c r="A430" t="n">
         <v>428</v>
       </c>
       <c r="B430" t="inlineStr">
@@ -33140,7 +33128,7 @@
       </c>
     </row>
     <row r="431">
-      <c r="A431" s="1" t="n">
+      <c r="A431" t="n">
         <v>429</v>
       </c>
       <c r="B431" t="inlineStr">
@@ -33216,7 +33204,7 @@
       </c>
     </row>
     <row r="432">
-      <c r="A432" s="1" t="n">
+      <c r="A432" t="n">
         <v>430</v>
       </c>
       <c r="B432" t="inlineStr">
@@ -33292,7 +33280,7 @@
       </c>
     </row>
     <row r="433">
-      <c r="A433" s="1" t="n">
+      <c r="A433" t="n">
         <v>431</v>
       </c>
       <c r="B433" t="inlineStr">
@@ -33368,7 +33356,7 @@
       </c>
     </row>
     <row r="434">
-      <c r="A434" s="1" t="n">
+      <c r="A434" t="n">
         <v>432</v>
       </c>
       <c r="B434" t="inlineStr">
@@ -33444,7 +33432,7 @@
       </c>
     </row>
     <row r="435">
-      <c r="A435" s="1" t="n">
+      <c r="A435" t="n">
         <v>433</v>
       </c>
       <c r="B435" t="inlineStr">
@@ -33520,7 +33508,7 @@
       </c>
     </row>
     <row r="436">
-      <c r="A436" s="1" t="n">
+      <c r="A436" t="n">
         <v>434</v>
       </c>
       <c r="B436" t="inlineStr">
@@ -33596,7 +33584,7 @@
       </c>
     </row>
     <row r="437">
-      <c r="A437" s="1" t="n">
+      <c r="A437" t="n">
         <v>435</v>
       </c>
       <c r="B437" t="inlineStr">
@@ -33672,7 +33660,7 @@
       </c>
     </row>
     <row r="438">
-      <c r="A438" s="1" t="n">
+      <c r="A438" t="n">
         <v>436</v>
       </c>
       <c r="B438" t="inlineStr">
@@ -33748,7 +33736,7 @@
       </c>
     </row>
     <row r="439">
-      <c r="A439" s="1" t="n">
+      <c r="A439" t="n">
         <v>437</v>
       </c>
       <c r="B439" t="inlineStr">
@@ -33824,7 +33812,7 @@
       </c>
     </row>
     <row r="440">
-      <c r="A440" s="1" t="n">
+      <c r="A440" t="n">
         <v>438</v>
       </c>
       <c r="B440" t="inlineStr">
@@ -33900,7 +33888,7 @@
       </c>
     </row>
     <row r="441">
-      <c r="A441" s="1" t="n">
+      <c r="A441" t="n">
         <v>439</v>
       </c>
       <c r="B441" t="inlineStr">
@@ -33976,7 +33964,7 @@
       </c>
     </row>
     <row r="442">
-      <c r="A442" s="1" t="n">
+      <c r="A442" t="n">
         <v>440</v>
       </c>
       <c r="B442" t="inlineStr">
@@ -34052,7 +34040,7 @@
       </c>
     </row>
     <row r="443">
-      <c r="A443" s="1" t="n">
+      <c r="A443" t="n">
         <v>441</v>
       </c>
       <c r="B443" t="inlineStr">
@@ -34128,7 +34116,7 @@
       </c>
     </row>
     <row r="444">
-      <c r="A444" s="1" t="n">
+      <c r="A444" t="n">
         <v>442</v>
       </c>
       <c r="B444" t="inlineStr">
@@ -34204,7 +34192,7 @@
       </c>
     </row>
     <row r="445">
-      <c r="A445" s="1" t="n">
+      <c r="A445" t="n">
         <v>443</v>
       </c>
       <c r="B445" t="inlineStr">
@@ -34280,7 +34268,7 @@
       </c>
     </row>
     <row r="446">
-      <c r="A446" s="1" t="n">
+      <c r="A446" t="n">
         <v>444</v>
       </c>
       <c r="B446" t="inlineStr">
@@ -34356,7 +34344,7 @@
       </c>
     </row>
     <row r="447">
-      <c r="A447" s="1" t="n">
+      <c r="A447" t="n">
         <v>445</v>
       </c>
       <c r="B447" t="inlineStr">
@@ -34432,7 +34420,7 @@
       </c>
     </row>
     <row r="448">
-      <c r="A448" s="1" t="n">
+      <c r="A448" t="n">
         <v>446</v>
       </c>
       <c r="B448" t="inlineStr">
@@ -34508,7 +34496,7 @@
       </c>
     </row>
     <row r="449">
-      <c r="A449" s="1" t="n">
+      <c r="A449" t="n">
         <v>447</v>
       </c>
       <c r="B449" t="inlineStr">
@@ -34584,7 +34572,7 @@
       </c>
     </row>
     <row r="450">
-      <c r="A450" s="1" t="n">
+      <c r="A450" t="n">
         <v>448</v>
       </c>
       <c r="B450" t="inlineStr">
@@ -34660,7 +34648,7 @@
       </c>
     </row>
     <row r="451">
-      <c r="A451" s="1" t="n">
+      <c r="A451" t="n">
         <v>449</v>
       </c>
       <c r="B451" t="inlineStr">
@@ -34736,7 +34724,7 @@
       </c>
     </row>
     <row r="452">
-      <c r="A452" s="1" t="n">
+      <c r="A452" t="n">
         <v>450</v>
       </c>
       <c r="B452" t="inlineStr">
@@ -34812,7 +34800,7 @@
       </c>
     </row>
     <row r="453">
-      <c r="A453" s="1" t="n">
+      <c r="A453" t="n">
         <v>451</v>
       </c>
       <c r="B453" t="inlineStr">
@@ -34888,7 +34876,7 @@
       </c>
     </row>
     <row r="454">
-      <c r="A454" s="1" t="n">
+      <c r="A454" t="n">
         <v>452</v>
       </c>
       <c r="B454" t="inlineStr">
@@ -34964,7 +34952,7 @@
       </c>
     </row>
     <row r="455">
-      <c r="A455" s="1" t="n">
+      <c r="A455" t="n">
         <v>453</v>
       </c>
       <c r="B455" t="inlineStr">
@@ -35040,7 +35028,7 @@
       </c>
     </row>
     <row r="456">
-      <c r="A456" s="1" t="n">
+      <c r="A456" t="n">
         <v>454</v>
       </c>
       <c r="B456" t="inlineStr">
@@ -35116,7 +35104,7 @@
       </c>
     </row>
     <row r="457">
-      <c r="A457" s="1" t="n">
+      <c r="A457" t="n">
         <v>455</v>
       </c>
       <c r="B457" t="inlineStr">
@@ -35192,7 +35180,7 @@
       </c>
     </row>
     <row r="458">
-      <c r="A458" s="1" t="n">
+      <c r="A458" t="n">
         <v>456</v>
       </c>
       <c r="B458" t="inlineStr">
@@ -35268,7 +35256,7 @@
       </c>
     </row>
     <row r="459">
-      <c r="A459" s="1" t="n">
+      <c r="A459" t="n">
         <v>457</v>
       </c>
       <c r="B459" t="inlineStr">
@@ -35344,7 +35332,7 @@
       </c>
     </row>
     <row r="460">
-      <c r="A460" s="1" t="n">
+      <c r="A460" t="n">
         <v>458</v>
       </c>
       <c r="B460" t="inlineStr">
@@ -35420,7 +35408,7 @@
       </c>
     </row>
     <row r="461">
-      <c r="A461" s="1" t="n">
+      <c r="A461" t="n">
         <v>459</v>
       </c>
       <c r="B461" t="inlineStr">
@@ -35496,7 +35484,7 @@
       </c>
     </row>
     <row r="462">
-      <c r="A462" s="1" t="n">
+      <c r="A462" t="n">
         <v>460</v>
       </c>
       <c r="B462" t="inlineStr">
@@ -35572,7 +35560,7 @@
       </c>
     </row>
     <row r="463">
-      <c r="A463" s="1" t="n">
+      <c r="A463" t="n">
         <v>461</v>
       </c>
       <c r="B463" t="inlineStr">
@@ -35648,7 +35636,7 @@
       </c>
     </row>
     <row r="464">
-      <c r="A464" s="1" t="n">
+      <c r="A464" t="n">
         <v>462</v>
       </c>
       <c r="B464" t="inlineStr">
@@ -35724,7 +35712,7 @@
       </c>
     </row>
     <row r="465">
-      <c r="A465" s="1" t="n">
+      <c r="A465" t="n">
         <v>463</v>
       </c>
       <c r="B465" t="inlineStr">
@@ -35800,7 +35788,7 @@
       </c>
     </row>
     <row r="466">
-      <c r="A466" s="1" t="n">
+      <c r="A466" t="n">
         <v>464</v>
       </c>
       <c r="B466" t="inlineStr">
@@ -35876,7 +35864,7 @@
       </c>
     </row>
     <row r="467">
-      <c r="A467" s="1" t="n">
+      <c r="A467" t="n">
         <v>465</v>
       </c>
       <c r="B467" t="inlineStr">
@@ -35952,7 +35940,7 @@
       </c>
     </row>
     <row r="468">
-      <c r="A468" s="1" t="n">
+      <c r="A468" t="n">
         <v>466</v>
       </c>
       <c r="B468" t="inlineStr">
@@ -36028,7 +36016,7 @@
       </c>
     </row>
     <row r="469">
-      <c r="A469" s="1" t="n">
+      <c r="A469" t="n">
         <v>467</v>
       </c>
       <c r="B469" t="inlineStr">
@@ -36104,7 +36092,7 @@
       </c>
     </row>
     <row r="470">
-      <c r="A470" s="1" t="n">
+      <c r="A470" t="n">
         <v>468</v>
       </c>
       <c r="B470" t="inlineStr">
@@ -36180,7 +36168,7 @@
       </c>
     </row>
     <row r="471">
-      <c r="A471" s="1" t="n">
+      <c r="A471" t="n">
         <v>469</v>
       </c>
       <c r="B471" t="inlineStr">
@@ -36256,7 +36244,7 @@
       </c>
     </row>
     <row r="472">
-      <c r="A472" s="1" t="n">
+      <c r="A472" t="n">
         <v>470</v>
       </c>
       <c r="B472" t="inlineStr">
@@ -36332,7 +36320,7 @@
       </c>
     </row>
     <row r="473">
-      <c r="A473" s="1" t="n">
+      <c r="A473" t="n">
         <v>471</v>
       </c>
       <c r="B473" t="inlineStr">
@@ -36408,7 +36396,7 @@
       </c>
     </row>
     <row r="474">
-      <c r="A474" s="1" t="n">
+      <c r="A474" t="n">
         <v>472</v>
       </c>
       <c r="B474" t="inlineStr">
@@ -36484,7 +36472,7 @@
       </c>
     </row>
     <row r="475">
-      <c r="A475" s="1" t="n">
+      <c r="A475" t="n">
         <v>473</v>
       </c>
       <c r="B475" t="inlineStr">
@@ -36560,7 +36548,7 @@
       </c>
     </row>
     <row r="476">
-      <c r="A476" s="1" t="n">
+      <c r="A476" t="n">
         <v>474</v>
       </c>
       <c r="B476" t="inlineStr">
@@ -36636,7 +36624,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="1" t="n">
+      <c r="A477" t="n">
         <v>475</v>
       </c>
       <c r="B477" t="inlineStr">
@@ -36712,7 +36700,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="1" t="n">
+      <c r="A478" t="n">
         <v>476</v>
       </c>
       <c r="B478" t="inlineStr">
@@ -36788,7 +36776,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="1" t="n">
+      <c r="A479" t="n">
         <v>477</v>
       </c>
       <c r="B479" t="inlineStr">
@@ -36864,7 +36852,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="1" t="n">
+      <c r="A480" t="n">
         <v>478</v>
       </c>
       <c r="B480" t="inlineStr">
@@ -36940,7 +36928,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="1" t="n">
+      <c r="A481" t="n">
         <v>479</v>
       </c>
       <c r="B481" t="inlineStr">
@@ -37016,7 +37004,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="1" t="n">
+      <c r="A482" t="n">
         <v>480</v>
       </c>
       <c r="B482" t="inlineStr">
@@ -37092,7 +37080,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="1" t="n">
+      <c r="A483" t="n">
         <v>481</v>
       </c>
       <c r="B483" t="inlineStr">
@@ -37168,7 +37156,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="1" t="n">
+      <c r="A484" t="n">
         <v>482</v>
       </c>
       <c r="B484" t="inlineStr">
@@ -37244,7 +37232,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="1" t="n">
+      <c r="A485" t="n">
         <v>483</v>
       </c>
       <c r="B485" t="inlineStr">
@@ -37320,7 +37308,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="1" t="n">
+      <c r="A486" t="n">
         <v>484</v>
       </c>
       <c r="B486" t="inlineStr">
@@ -37396,7 +37384,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="1" t="n">
+      <c r="A487" t="n">
         <v>485</v>
       </c>
       <c r="B487" t="inlineStr">
@@ -37472,7 +37460,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="1" t="n">
+      <c r="A488" t="n">
         <v>486</v>
       </c>
       <c r="B488" t="inlineStr">
@@ -37548,7 +37536,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="1" t="n">
+      <c r="A489" t="n">
         <v>487</v>
       </c>
       <c r="B489" t="inlineStr">
@@ -37624,7 +37612,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="1" t="n">
+      <c r="A490" t="n">
         <v>488</v>
       </c>
       <c r="B490" t="inlineStr">
@@ -37700,7 +37688,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="1" t="n">
+      <c r="A491" t="n">
         <v>489</v>
       </c>
       <c r="B491" t="inlineStr">
@@ -37776,7 +37764,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="1" t="n">
+      <c r="A492" t="n">
         <v>490</v>
       </c>
       <c r="B492" t="inlineStr">
@@ -37852,7 +37840,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="1" t="n">
+      <c r="A493" t="n">
         <v>491</v>
       </c>
       <c r="B493" t="inlineStr">
@@ -37928,7 +37916,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="1" t="n">
+      <c r="A494" t="n">
         <v>492</v>
       </c>
       <c r="B494" t="inlineStr">
@@ -38004,7 +37992,7 @@
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="1" t="n">
+      <c r="A495" t="n">
         <v>493</v>
       </c>
       <c r="B495" t="inlineStr">
@@ -38080,7 +38068,7 @@
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="1" t="n">
+      <c r="A496" t="n">
         <v>494</v>
       </c>
       <c r="B496" t="inlineStr">
@@ -38156,7 +38144,7 @@
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="1" t="n">
+      <c r="A497" t="n">
         <v>495</v>
       </c>
       <c r="B497" t="inlineStr">
@@ -38232,7 +38220,7 @@
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="1" t="n">
+      <c r="A498" t="n">
         <v>496</v>
       </c>
       <c r="B498" t="inlineStr">
@@ -38308,7 +38296,7 @@
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="1" t="n">
+      <c r="A499" t="n">
         <v>497</v>
       </c>
       <c r="B499" t="inlineStr">
@@ -38384,7 +38372,7 @@
       </c>
     </row>
     <row r="500">
-      <c r="A500" s="1" t="n">
+      <c r="A500" t="n">
         <v>498</v>
       </c>
       <c r="B500" t="inlineStr">
@@ -38460,7 +38448,7 @@
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="1" t="n">
+      <c r="A501" t="n">
         <v>499</v>
       </c>
       <c r="B501" t="inlineStr">
@@ -38536,7 +38524,7 @@
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="1" t="n">
+      <c r="A502" t="n">
         <v>500</v>
       </c>
       <c r="B502" t="inlineStr">
@@ -38612,7 +38600,7 @@
       </c>
     </row>
     <row r="503">
-      <c r="A503" s="1" t="n">
+      <c r="A503" t="n">
         <v>501</v>
       </c>
       <c r="B503" t="inlineStr">
@@ -38688,7 +38676,7 @@
       </c>
     </row>
     <row r="504">
-      <c r="A504" s="1" t="n">
+      <c r="A504" t="n">
         <v>502</v>
       </c>
       <c r="B504" t="inlineStr">
@@ -38764,7 +38752,7 @@
       </c>
     </row>
     <row r="505">
-      <c r="A505" s="1" t="n">
+      <c r="A505" t="n">
         <v>503</v>
       </c>
       <c r="B505" t="inlineStr">
@@ -38840,7 +38828,7 @@
       </c>
     </row>
     <row r="506">
-      <c r="A506" s="1" t="n">
+      <c r="A506" t="n">
         <v>504</v>
       </c>
       <c r="B506" t="inlineStr">
@@ -38916,7 +38904,7 @@
       </c>
     </row>
     <row r="507">
-      <c r="A507" s="1" t="n">
+      <c r="A507" t="n">
         <v>505</v>
       </c>
       <c r="B507" t="inlineStr">
@@ -38992,7 +38980,7 @@
       </c>
     </row>
     <row r="508">
-      <c r="A508" s="1" t="n">
+      <c r="A508" t="n">
         <v>506</v>
       </c>
       <c r="B508" t="inlineStr">
@@ -39068,7 +39056,7 @@
       </c>
     </row>
     <row r="509">
-      <c r="A509" s="1" t="n">
+      <c r="A509" t="n">
         <v>507</v>
       </c>
       <c r="B509" t="inlineStr">
@@ -39144,7 +39132,7 @@
       </c>
     </row>
     <row r="510">
-      <c r="A510" s="1" t="n">
+      <c r="A510" t="n">
         <v>508</v>
       </c>
       <c r="B510" t="inlineStr">
@@ -39220,7 +39208,7 @@
       </c>
     </row>
     <row r="511">
-      <c r="A511" s="1" t="n">
+      <c r="A511" t="n">
         <v>509</v>
       </c>
       <c r="B511" t="inlineStr">
@@ -39296,7 +39284,7 @@
       </c>
     </row>
     <row r="512">
-      <c r="A512" s="1" t="n">
+      <c r="A512" t="n">
         <v>510</v>
       </c>
       <c r="B512" t="inlineStr">
@@ -39372,7 +39360,7 @@
       </c>
     </row>
     <row r="513">
-      <c r="A513" s="1" t="n">
+      <c r="A513" t="n">
         <v>511</v>
       </c>
       <c r="B513" t="inlineStr">
@@ -39448,7 +39436,7 @@
       </c>
     </row>
     <row r="514">
-      <c r="A514" s="1" t="n">
+      <c r="A514" t="n">
         <v>512</v>
       </c>
       <c r="B514" t="inlineStr">
@@ -39524,7 +39512,7 @@
       </c>
     </row>
     <row r="515">
-      <c r="A515" s="1" t="n">
+      <c r="A515" t="n">
         <v>513</v>
       </c>
       <c r="B515" t="inlineStr">
@@ -39600,7 +39588,7 @@
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="1" t="n">
+      <c r="A516" t="n">
         <v>514</v>
       </c>
       <c r="B516" t="inlineStr">
@@ -39676,7 +39664,7 @@
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="1" t="n">
+      <c r="A517" t="n">
         <v>515</v>
       </c>
       <c r="B517" t="inlineStr">
@@ -39752,7 +39740,7 @@
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="1" t="n">
+      <c r="A518" t="n">
         <v>516</v>
       </c>
       <c r="B518" t="inlineStr">
@@ -39828,7 +39816,7 @@
       </c>
     </row>
     <row r="519">
-      <c r="A519" s="1" t="n">
+      <c r="A519" t="n">
         <v>517</v>
       </c>
       <c r="B519" t="inlineStr">
@@ -39904,7 +39892,7 @@
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="1" t="n">
+      <c r="A520" t="n">
         <v>518</v>
       </c>
       <c r="B520" t="inlineStr">
@@ -39980,7 +39968,7 @@
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="1" t="n">
+      <c r="A521" t="n">
         <v>519</v>
       </c>
       <c r="B521" t="inlineStr">
@@ -40056,7 +40044,7 @@
       </c>
     </row>
     <row r="522">
-      <c r="A522" s="1" t="n">
+      <c r="A522" t="n">
         <v>520</v>
       </c>
       <c r="B522" t="inlineStr">
@@ -40132,7 +40120,7 @@
       </c>
     </row>
     <row r="523">
-      <c r="A523" s="1" t="n">
+      <c r="A523" t="n">
         <v>521</v>
       </c>
       <c r="B523" t="inlineStr">
@@ -40208,7 +40196,7 @@
       </c>
     </row>
     <row r="524">
-      <c r="A524" s="1" t="n">
+      <c r="A524" t="n">
         <v>522</v>
       </c>
       <c r="B524" t="inlineStr">
@@ -40284,7 +40272,7 @@
       </c>
     </row>
     <row r="525">
-      <c r="A525" s="1" t="n">
+      <c r="A525" t="n">
         <v>523</v>
       </c>
       <c r="B525" t="inlineStr">
@@ -40360,7 +40348,7 @@
       </c>
     </row>
     <row r="526">
-      <c r="A526" s="1" t="n">
+      <c r="A526" t="n">
         <v>524</v>
       </c>
       <c r="B526" t="inlineStr">
@@ -40436,7 +40424,7 @@
       </c>
     </row>
     <row r="527">
-      <c r="A527" s="1" t="n">
+      <c r="A527" t="n">
         <v>525</v>
       </c>
       <c r="B527" t="inlineStr">
@@ -40512,7 +40500,7 @@
       </c>
     </row>
     <row r="528">
-      <c r="A528" s="1" t="n">
+      <c r="A528" t="n">
         <v>526</v>
       </c>
       <c r="B528" t="inlineStr">
@@ -40588,7 +40576,7 @@
       </c>
     </row>
     <row r="529">
-      <c r="A529" s="1" t="n">
+      <c r="A529" t="n">
         <v>527</v>
       </c>
       <c r="B529" t="inlineStr">
